--- a/data/trans_dic/P15D$consultar-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15D$consultar-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital)</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital) (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,61</t>
+          <t>0,0; 37,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 30,57</t>
+          <t>2,6; 28,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 38,13</t>
+          <t>4,41; 39,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,21</t>
+          <t>0,0; 22,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,49</t>
+          <t>0,0; 57,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,52</t>
+          <t>0,0; 34,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,15</t>
+          <t>0,0; 31,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,53; 33,32</t>
+          <t>7,33; 33,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,29</t>
+          <t>0,0; 32,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 23,87</t>
+          <t>3,62; 23,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 29,04</t>
+          <t>4,84; 26,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 20,21</t>
+          <t>5,09; 21,38</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,57</t>
+          <t>0,0; 42,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,61; 33,86</t>
+          <t>5,58; 30,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 40,26</t>
+          <t>5,37; 40,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 18,94</t>
+          <t>0,65; 20,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,91</t>
+          <t>0,0; 62,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,6</t>
+          <t>0,0; 30,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,85</t>
+          <t>0,0; 24,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,81; 43,02</t>
+          <t>13,44; 46,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 37,59</t>
+          <t>4,45; 38,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 24,85</t>
+          <t>5,26; 24,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 22,95</t>
+          <t>2,49; 22,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,36; 27,67</t>
+          <t>8,37; 30,01</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 33,98</t>
+          <t>6,56; 34,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 14,73</t>
+          <t>1,64; 15,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,92; 33,51</t>
+          <t>5,94; 33,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 26,65</t>
+          <t>4,05; 27,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 49,82</t>
+          <t>6,62; 53,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,74</t>
+          <t>0,0; 70,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,54; 53,22</t>
+          <t>11,98; 57,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,47; 29,41</t>
+          <t>5,24; 30,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 17,47</t>
+          <t>3,15; 17,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,02; 33,92</t>
+          <t>8,09; 35,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,92; 27,72</t>
+          <t>9,49; 30,0</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 24,61</t>
+          <t>2,59; 23,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,54</t>
+          <t>1,05; 10,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 25,09</t>
+          <t>6,42; 23,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 18,77</t>
+          <t>3,55; 20,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,63; 42,43</t>
+          <t>8,35; 42,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,27; 23,94</t>
+          <t>5,74; 25,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 30,15</t>
+          <t>8,08; 30,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,97; 25,09</t>
+          <t>6,73; 25,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 12,79</t>
+          <t>3,41; 12,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 15,33</t>
+          <t>4,06; 14,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 20,54</t>
+          <t>7,37; 20,19</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,32</t>
+          <t>0,0; 58,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 23,78</t>
+          <t>2,66; 24,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 25,39</t>
+          <t>5,73; 26,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 32,93</t>
+          <t>2,37; 33,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,22</t>
+          <t>0,0; 38,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 17,5</t>
+          <t>3,34; 17,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,54; 36,35</t>
+          <t>11,75; 38,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,83; 30,29</t>
+          <t>13,86; 31,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 33,03</t>
+          <t>3,0; 31,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 17,42</t>
+          <t>4,38; 15,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,13; 26,83</t>
+          <t>10,51; 27,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,77; 25,43</t>
+          <t>10,59; 27,07</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,07</t>
+          <t>0,0; 36,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,47; 30,93</t>
+          <t>3,56; 31,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,69; 29,74</t>
+          <t>3,68; 27,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,53</t>
+          <t>1,06; 8,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,15; 18,15</t>
+          <t>3,28; 19,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,43; 21,81</t>
+          <t>6,77; 21,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,43; 25,21</t>
+          <t>4,38; 24,85</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,45; 11,49</t>
+          <t>2,45; 11,64</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 13,04</t>
+          <t>2,14; 12,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,47; 17,94</t>
+          <t>5,35; 18,03</t>
         </is>
       </c>
     </row>
@@ -1557,57 +1557,57 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,56; 20,78</t>
+          <t>8,03; 20,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,43; 11,82</t>
+          <t>5,15; 11,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,44; 18,12</t>
+          <t>8,8; 18,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,25; 14,07</t>
+          <t>5,25; 14,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,93; 22,56</t>
+          <t>7,27; 21,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,48; 12,97</t>
+          <t>5,32; 12,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,21; 15,18</t>
+          <t>6,63; 15,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,95; 24,06</t>
+          <t>14,88; 24,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,85; 18,63</t>
+          <t>9,11; 19,14</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,28; 11,4</t>
+          <t>6,03; 11,18</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,54; 15,16</t>
+          <t>8,61; 14,69</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital)</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital) (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4864</t>
+          <t>0; 4783</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>899; 10382</t>
+          <t>884; 9828</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>925; 8212</t>
+          <t>951; 8460</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5055</t>
+          <t>0; 5361</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4461</t>
+          <t>0; 4452</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5981</t>
+          <t>0; 5966</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6453</t>
+          <t>0; 6243</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1981; 7733</t>
+          <t>1701; 7719</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6167</t>
+          <t>0; 6676</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1878; 12242</t>
+          <t>1857; 12148</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1940; 12082</t>
+          <t>2012; 11161</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2151; 9509</t>
+          <t>2395; 10059</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5122</t>
+          <t>0; 5681</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1819; 10987</t>
+          <t>1810; 9971</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>915; 6787</t>
+          <t>906; 6789</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>168; 4573</t>
+          <t>157; 4845</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4242</t>
+          <t>0; 3513</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 8753</t>
+          <t>0; 8278</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4383</t>
+          <t>0; 5498</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3198; 9964</t>
+          <t>3112; 10716</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>834; 7092</t>
+          <t>840; 7177</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3281; 14739</t>
+          <t>3117; 14491</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>972; 8938</t>
+          <t>970; 8731</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4426; 13091</t>
+          <t>3960; 14198</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1828; 9611</t>
+          <t>1857; 9725</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>897; 8345</t>
+          <t>931; 8618</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1838; 10410</t>
+          <t>1846; 10273</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1515; 8887</t>
+          <t>1349; 9163</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1516</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>881; 6975</t>
+          <t>926; 7487</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5520</t>
+          <t>0; 6200</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1505; 6386</t>
+          <t>1438; 6845</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1818; 9778</t>
+          <t>1743; 10074</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2183; 12338</t>
+          <t>2224; 12398</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3198; 13523</t>
+          <t>3225; 14170</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4042; 12569</t>
+          <t>4301; 13600</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1052; 9602</t>
+          <t>1010; 9069</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>988; 9124</t>
+          <t>1007; 10255</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4316; 14801</t>
+          <t>3787; 14002</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2182; 12483</t>
+          <t>2358; 13348</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2158; 10613</t>
+          <t>2088; 10664</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2078; 11652</t>
+          <t>2796; 12188</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1985</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4335; 14927</t>
+          <t>4000; 15163</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4462; 16066</t>
+          <t>4310; 16425</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5026; 18462</t>
+          <t>4921; 17937</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3856; 14937</t>
+          <t>3956; 14262</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7944; 23826</t>
+          <t>8554; 23418</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 7877</t>
+          <t>0; 7351</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1002; 9101</t>
+          <t>1018; 9536</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2338; 10559</t>
+          <t>2383; 11124</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>833; 12614</t>
+          <t>908; 12815</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 9477</t>
+          <t>0; 8621</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1922; 10190</t>
+          <t>1942; 10185</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4664; 14688</t>
+          <t>4747; 15499</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6817; 16093</t>
+          <t>7362; 16779</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1131; 11592</t>
+          <t>1052; 10976</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4111; 16809</t>
+          <t>4225; 15420</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8305; 21999</t>
+          <t>8616; 22536</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9844; 23256</t>
+          <t>9681; 24753</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5678</t>
+          <t>0; 5831</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>930; 8297</t>
+          <t>956; 8510</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2014</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3098</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1035; 8341</t>
+          <t>1032; 7583</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>947; 8507</t>
+          <t>943; 7988</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1904; 10967</t>
+          <t>1982; 11812</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2999; 10173</t>
+          <t>3160; 10076</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1959; 11152</t>
+          <t>1939; 10991</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2841; 13337</t>
+          <t>2844; 13508</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1907; 11736</t>
+          <t>1925; 11259</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2610; 10469</t>
+          <t>3121; 10524</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9225; 25358</t>
+          <t>9802; 24921</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15411; 33541</t>
+          <t>14609; 33785</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16848; 36178</t>
+          <t>17558; 36131</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10387; 27843</t>
+          <t>10380; 28251</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6496; 21166</t>
+          <t>6823; 20507</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13931; 32991</t>
+          <t>13536; 31420</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11817; 28885</t>
+          <t>12618; 29936</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31040; 49947</t>
+          <t>30888; 50287</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19109; 40199</t>
+          <t>19655; 41309</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33805; 61371</t>
+          <t>32422; 60169</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33298; 59107</t>
+          <t>33563; 57282</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>44994; 71286</t>
+          <t>45007; 71282</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$consultar-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15D$consultar-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,96</t>
+          <t>0,0; 35,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 28,94</t>
+          <t>2,62; 28,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 39,28</t>
+          <t>4,31; 36,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,49</t>
+          <t>0,0; 19,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,37</t>
+          <t>0,0; 56,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,43</t>
+          <t>0,0; 30,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,11</t>
+          <t>0,0; 31,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,33; 33,26</t>
+          <t>9,67; 35,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,79</t>
+          <t>0,0; 29,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 23,68</t>
+          <t>3,78; 23,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 26,82</t>
+          <t>6,38; 28,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,09; 21,38</t>
+          <t>5,73; 23,07</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,78</t>
+          <t>0,0; 47,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,58; 30,73</t>
+          <t>5,41; 31,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 40,26</t>
+          <t>5,36; 45,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 20,07</t>
+          <t>2,12; 25,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,86</t>
+          <t>0,0; 57,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,83</t>
+          <t>0,0; 32,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,89</t>
+          <t>0,0; 23,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,44; 46,27</t>
+          <t>12,51; 41,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 38,04</t>
+          <t>4,4; 35,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 24,44</t>
+          <t>6,1; 26,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 22,42</t>
+          <t>2,46; 22,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,37; 30,01</t>
+          <t>9,02; 29,05</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 34,38</t>
+          <t>6,46; 35,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 15,22</t>
+          <t>1,69; 15,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 33,07</t>
+          <t>6,19; 33,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 27,48</t>
+          <t>3,79; 25,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,62; 53,48</t>
+          <t>6,58; 51,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,47</t>
+          <t>0,0; 63,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,98; 57,05</t>
+          <t>12,35; 55,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 30,31</t>
+          <t>5,43; 28,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 17,55</t>
+          <t>4,0; 18,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,09; 35,55</t>
+          <t>7,98; 34,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,49; 30,0</t>
+          <t>8,59; 28,02</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -1137,32 +1137,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 23,24</t>
+          <t>2,69; 24,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 10,73</t>
+          <t>1,05; 9,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 23,74</t>
+          <t>6,46; 24,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 20,08</t>
+          <t>3,51; 18,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,35; 42,64</t>
+          <t>8,38; 42,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,74; 25,04</t>
+          <t>5,61; 23,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,27 +1172,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,08; 30,63</t>
+          <t>7,51; 29,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,73; 25,65</t>
+          <t>6,83; 25,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 12,43</t>
+          <t>3,5; 12,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 14,63</t>
+          <t>3,82; 14,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 20,19</t>
+          <t>6,78; 18,4</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,15</t>
+          <t>0,0; 54,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 24,91</t>
+          <t>2,67; 22,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 26,75</t>
+          <t>4,65; 25,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 33,45</t>
+          <t>2,34; 30,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,4</t>
+          <t>0,0; 33,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,34; 17,49</t>
+          <t>3,35; 18,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,75; 38,35</t>
+          <t>11,82; 38,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,86; 31,58</t>
+          <t>12,75; 30,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 31,28</t>
+          <t>3,05; 30,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 15,98</t>
+          <t>4,45; 17,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,51; 27,49</t>
+          <t>10,75; 27,19</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,59; 27,07</t>
+          <t>10,48; 25,61</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,01</t>
+          <t>0,0; 32,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,56; 31,72</t>
+          <t>3,48; 31,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,68; 27,04</t>
+          <t>3,61; 26,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 8,95</t>
+          <t>1,07; 9,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,28; 19,55</t>
+          <t>3,27; 19,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,77; 21,6</t>
+          <t>6,23; 19,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,38; 24,85</t>
+          <t>4,46; 23,65</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,45; 11,64</t>
+          <t>2,47; 11,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 12,51</t>
+          <t>2,2; 13,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,35; 18,03</t>
+          <t>4,56; 16,52</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,03; 20,42</t>
+          <t>8,25; 21,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,15; 11,91</t>
+          <t>5,12; 11,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,8; 18,1</t>
+          <t>8,81; 17,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,25; 14,28</t>
+          <t>5,06; 13,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,27; 21,86</t>
+          <t>6,55; 21,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,35</t>
+          <t>5,49; 12,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,63; 15,73</t>
+          <t>6,09; 15,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,88; 24,22</t>
+          <t>14,59; 23,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,11; 19,14</t>
+          <t>8,85; 18,45</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,03; 11,18</t>
+          <t>6,21; 11,2</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,61; 14,69</t>
+          <t>8,6; 15,22</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,1; 17,58</t>
+          <t>10,85; 16,84</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>6546</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4783</t>
+          <t>0; 4484</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>884; 9828</t>
+          <t>891; 9633</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>951; 8460</t>
+          <t>929; 7956</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5361</t>
+          <t>0; 5094</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4452</t>
+          <t>0; 4369</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5966</t>
+          <t>0; 5336</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6243</t>
+          <t>0; 6309</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1701; 7719</t>
+          <t>2533; 9374</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6676</t>
+          <t>0; 6094</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1857; 12148</t>
+          <t>1938; 12125</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2012; 11161</t>
+          <t>2655; 11762</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2395; 10059</t>
+          <t>2983; 12008</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>8792</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5681</t>
+          <t>0; 6327</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1810; 9971</t>
+          <t>1754; 10250</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>906; 6789</t>
+          <t>903; 7597</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>157; 4845</t>
+          <t>544; 6646</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3513</t>
+          <t>0; 3222</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 8278</t>
+          <t>0; 8699</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5498</t>
+          <t>0; 5259</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3112; 10716</t>
+          <t>3126; 10390</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>840; 7177</t>
+          <t>830; 6688</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3117; 14491</t>
+          <t>3616; 15486</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>970; 8731</t>
+          <t>958; 8794</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3960; 14198</t>
+          <t>4574; 14731</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7974</t>
+          <t>8143</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1857; 9725</t>
+          <t>1828; 9935</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>931; 8618</t>
+          <t>956; 8655</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1846; 10273</t>
+          <t>1924; 10477</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1349; 9163</t>
+          <t>1411; 9396</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2368,37 +2368,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>926; 7487</t>
+          <t>922; 7174</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6200</t>
+          <t>0; 5554</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1438; 6845</t>
+          <t>1567; 7016</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1743; 10074</t>
+          <t>1805; 9343</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2224; 12398</t>
+          <t>2827; 13178</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3225; 14170</t>
+          <t>3182; 13642</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4301; 13600</t>
+          <t>4292; 14001</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14540</t>
+          <t>15425</t>
         </is>
       </c>
     </row>
@@ -2551,32 +2551,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1010; 9069</t>
+          <t>1048; 9379</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1007; 10255</t>
+          <t>1004; 9120</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3787; 14002</t>
+          <t>3813; 14395</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2358; 13348</t>
+          <t>2733; 14090</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2088; 10664</t>
+          <t>2097; 10705</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2796; 12188</t>
+          <t>2730; 11311</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2586,27 +2586,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4000; 15163</t>
+          <t>4161; 16416</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4310; 16425</t>
+          <t>4376; 16038</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4921; 17937</t>
+          <t>5044; 17444</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3956; 14262</t>
+          <t>3726; 14209</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8554; 23418</t>
+          <t>9035; 24501</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15445</t>
+          <t>16226</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 7351</t>
+          <t>0; 6898</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1018; 9536</t>
+          <t>1021; 8537</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2383; 11124</t>
+          <t>1934; 10438</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>908; 12815</t>
+          <t>945; 12268</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 8621</t>
+          <t>0; 7531</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1942; 10185</t>
+          <t>1951; 11011</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4747; 15499</t>
+          <t>4776; 15642</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7362; 16779</t>
+          <t>7261; 17281</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1052; 10976</t>
+          <t>1069; 10845</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4225; 15420</t>
+          <t>4295; 16928</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8616; 22536</t>
+          <t>8813; 22293</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9681; 24753</t>
+          <t>10194; 24913</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5969</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5831</t>
+          <t>0; 5182</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>956; 8510</t>
+          <t>932; 8404</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1032; 7583</t>
+          <t>1013; 7520</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>943; 7988</t>
+          <t>954; 8050</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1982; 11812</t>
+          <t>1976; 11488</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3160; 10076</t>
+          <t>3066; 9725</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1939; 10991</t>
+          <t>1971; 10463</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2844; 13508</t>
+          <t>2865; 13243</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1925; 11259</t>
+          <t>1982; 12386</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3121; 10524</t>
+          <t>2756; 9982</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17157</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>39751</t>
+          <t>42255</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>56908</t>
+          <t>61101</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9802; 24921</t>
+          <t>10061; 25979</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14609; 33785</t>
+          <t>14526; 32864</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17558; 36131</t>
+          <t>17590; 35275</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10380; 28251</t>
+          <t>11031; 29413</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6823; 20507</t>
+          <t>6149; 20042</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13536; 31420</t>
+          <t>13971; 31828</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12618; 29936</t>
+          <t>11592; 29343</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>30888; 50287</t>
+          <t>32881; 53367</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19655; 41309</t>
+          <t>19093; 39821</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32422; 60169</t>
+          <t>33423; 60281</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33563; 57282</t>
+          <t>33532; 59360</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>45007; 71282</t>
+          <t>48112; 74691</t>
         </is>
       </c>
     </row>
